--- a/Methodology/PIRNN/03-PWM-Y/Ts-03/Resumo_Estatisticas.xlsx
+++ b/Methodology/PIRNN/03-PWM-Y/Ts-03/Resumo_Estatisticas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Todos_Modelos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Top_10_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Top_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Melhor_Modelo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +477,7 @@
         <v>0.7225162384391202</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3251396180375515</v>
+        <v>0.3251396180375516</v>
       </c>
       <c r="E2" t="n">
         <v>0.02325202134550686</v>
@@ -497,7 +498,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.61861046327906</v>
+        <v>-1.618610463279059</v>
       </c>
       <c r="D3" t="n">
         <v>2.54820621643472</v>
@@ -527,7 +528,7 @@
         <v>1.498550083041004</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0982356604637311</v>
+        <v>0.09823566046373108</v>
       </c>
       <c r="F4" t="n">
         <v>0.1115669914223883</v>
@@ -545,7 +546,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6776829213689601</v>
+        <v>0.67768292136896</v>
       </c>
       <c r="D5" t="n">
         <v>0.3311947343199603</v>
@@ -593,7 +594,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.5713472279828367</v>
+        <v>-0.5713472279828364</v>
       </c>
       <c r="D7" t="n">
         <v>1.814721188954887</v>
@@ -798,4 +799,195 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Neurons</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Best_R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>model_32_Ld0.7_Lp0.3_r0.01_seed0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[32]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9839536697793403</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>model_16_8_Ld0.7_Lp0.3_r0.9_seed1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[16, 8]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7081942251788943</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>model_264_128_Ld0.3_Lp0.7_r0.9_seed2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9758126271306991</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>model_264_128_Ld0.7_Lp0.3_r0.5_seed1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9623620580899729</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Test_2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>model_8_4_Ld0.7_Lp0.3_r0.5_seed0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[8, 4]</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7286890281357081</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Test_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>model_32_Ld0.3_Lp0.7_r0.9_seed0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[32]</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9124910241313141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>